--- a/excel-files/atlas-mitigations.xlsx
+++ b/excel-files/atlas-mitigations.xlsx
@@ -2303,16 +2303,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2335,7 +2327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2343,35 +2335,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2671,28 +2645,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2709,7 +2683,7 @@
       <c r="D2" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>148</v>
       </c>
       <c r="F2" t="s">
@@ -2732,7 +2706,7 @@
       <c r="D3" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>149</v>
       </c>
       <c r="F3" t="s">
@@ -2755,7 +2729,7 @@
       <c r="D4" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>150</v>
       </c>
       <c r="F4" t="s">
@@ -2778,7 +2752,7 @@
       <c r="D5" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>151</v>
       </c>
       <c r="F5" t="s">
@@ -2801,7 +2775,7 @@
       <c r="D6" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>152</v>
       </c>
       <c r="F6" t="s">
@@ -2824,7 +2798,7 @@
       <c r="D7" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F7" t="s">
@@ -2847,7 +2821,7 @@
       <c r="D8" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F8" t="s">
@@ -2870,7 +2844,7 @@
       <c r="D9" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>155</v>
       </c>
       <c r="F9" t="s">
@@ -2893,7 +2867,7 @@
       <c r="D10" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F10" t="s">
@@ -2916,7 +2890,7 @@
       <c r="D11" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>157</v>
       </c>
       <c r="F11" t="s">
@@ -2939,7 +2913,7 @@
       <c r="D12" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>158</v>
       </c>
       <c r="F12" t="s">
@@ -2962,7 +2936,7 @@
       <c r="D13" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>159</v>
       </c>
       <c r="F13" t="s">
@@ -2985,7 +2959,7 @@
       <c r="D14" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F14" t="s">
@@ -3008,7 +2982,7 @@
       <c r="D15" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>161</v>
       </c>
       <c r="F15" t="s">
@@ -3031,7 +3005,7 @@
       <c r="D16" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F16" t="s">
@@ -3054,7 +3028,7 @@
       <c r="D17" t="s">
         <v>128</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>163</v>
       </c>
       <c r="F17" t="s">
@@ -3077,7 +3051,7 @@
       <c r="D18" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>164</v>
       </c>
       <c r="F18" t="s">
@@ -3100,7 +3074,7 @@
       <c r="D19" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>165</v>
       </c>
       <c r="F19" t="s">
@@ -3123,7 +3097,7 @@
       <c r="D20" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>166</v>
       </c>
       <c r="F20" t="s">
@@ -3146,7 +3120,7 @@
       <c r="D21" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>167</v>
       </c>
       <c r="F21" t="s">
@@ -3169,7 +3143,7 @@
       <c r="D22" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>168</v>
       </c>
       <c r="F22" t="s">
@@ -3192,7 +3166,7 @@
       <c r="D23" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F23" t="s">
@@ -3215,7 +3189,7 @@
       <c r="D24" t="s">
         <v>135</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F24" t="s">
@@ -3238,7 +3212,7 @@
       <c r="D25" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>171</v>
       </c>
       <c r="F25" t="s">
@@ -3261,7 +3235,7 @@
       <c r="D26" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>172</v>
       </c>
       <c r="F26" t="s">
@@ -3284,7 +3258,7 @@
       <c r="D27" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>173</v>
       </c>
       <c r="F27" t="s">
@@ -3307,7 +3281,7 @@
       <c r="D28" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>174</v>
       </c>
       <c r="F28" t="s">
@@ -3330,7 +3304,7 @@
       <c r="D29" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>175</v>
       </c>
       <c r="F29" t="s">
@@ -3353,7 +3327,7 @@
       <c r="D30" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="1" t="s">
         <v>176</v>
       </c>
       <c r="F30" t="s">
@@ -3376,7 +3350,7 @@
       <c r="D31" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="1" t="s">
         <v>177</v>
       </c>
       <c r="F31" t="s">
@@ -3399,7 +3373,7 @@
       <c r="D32" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="1" t="s">
         <v>178</v>
       </c>
       <c r="F32" t="s">
@@ -3422,7 +3396,7 @@
       <c r="D33" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>179</v>
       </c>
       <c r="F33" t="s">
@@ -3445,7 +3419,7 @@
       <c r="D34" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="1" t="s">
         <v>180</v>
       </c>
       <c r="F34" t="s">
@@ -3468,7 +3442,7 @@
       <c r="D35" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="1" t="s">
         <v>181</v>
       </c>
       <c r="F35" t="s">
@@ -3491,7 +3465,7 @@
       <c r="D36" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="1" t="s">
         <v>182</v>
       </c>
       <c r="F36" t="s">
@@ -3549,43 +3523,43 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>200</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/excel-files/atlas-mitigations.xlsx
+++ b/excel-files/atlas-mitigations.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="735">
   <si>
     <t>ID</t>
   </si>
@@ -368,7 +368,7 @@
 Also consider computing features in the cloud to prevent gray-box attacks, where an adversary has access to the model preprocessing methods.</t>
   </si>
   <si>
-    <t>Implement logging of inputs and outputs of deployed AI models. When deploying AI agents, implement logging of the intermediate steps of agentic actions and decisions, data access and tool use, and identity of the agent. Monitoring logs can help to detect security threats and mitigate impacts.
+    <t>Implement logging of inputs and outputs of deployed AI models. When deploying AI agents, implement logging of the intermediate steps of agentic actions and decisions, data access and tool use, installation commands, and identity of the agent. Monitoring logs can help to detect security threats and mitigate impacts.
 Additionally, having logging enabled can discourage adversaries who want to remain undetected from utilizing AI resources.</t>
   </si>
   <si>
@@ -376,7 +376,7 @@
 Incorporate adversarial detection algorithms into the AI system prior to the AI model.</t>
   </si>
   <si>
-    <t>Enforce binary and application integrity with digital signature verification to prevent untrusted code from executing. Adversaries can embed malicious code in AI software or models. Enforcement of code signing can prevent the compromise of the AI supply chain and prevent execution of malicious code.</t>
+    <t>Enforce binary and application integrity with digital signature verification to prevent untrusted code from executing. Adversaries can embed malicious code in AI software or models. Developers should also cryptographically sign SBOM and AIBOM components that track model or data provenance. Enforcement of code signing can prevent the compromise of the AI supply chain and prevent execution of malicious code.</t>
   </si>
   <si>
     <t xml:space="preserve">Establish access controls on internal model registries and limit internal access to production models. Limit access to training data only to approved users.
@@ -460,7 +460,7 @@
 </t>
   </si>
   <si>
-    <t>Define security boundaries around agentic tools and data sources with methods such as API access, container isolation, code execution sandboxing, and rate limiting of tool invocation. This restricts untrusted processes or potential compromises from spreading throughout the system.</t>
+    <t>Define security boundaries around agentic tools and data sources with methods such as API access, container isolation, code execution sandboxing, and rate limiting of tool invocation. When sandboxing, limit resource and network access and build the container or virtual machine from a clean base image before each run. This restricts untrusted processes or potential compromises from spreading throughout the system.</t>
   </si>
   <si>
     <t>When deploying an AI agent that acts as a representative of a user and performs actions on their behalf, it is important to implement robust policies and controls on permissions and lifecycle management of the agent. Lifecycle management involves establishing identity, protocols for access management, and decommissioning of the agent when its role is no longer needed. Controls should also include the principle of least privilege and delegated access from the user account. When acting as a representative of a user, the AI agent should not be granted permissions that the user would not be granted within the system or organization.</t>
@@ -613,6 +613,9 @@
   </si>
   <si>
     <t>23 December 2025</t>
+  </si>
+  <si>
+    <t>19 March 2026</t>
   </si>
   <si>
     <t>18 December 2025</t>
@@ -2303,8 +2306,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2327,7 +2338,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2335,17 +2346,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2645,28 +2674,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2683,7 +2712,7 @@
       <c r="D2" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F2" t="s">
@@ -2706,7 +2735,7 @@
       <c r="D3" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F3" t="s">
@@ -2729,7 +2758,7 @@
       <c r="D4" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>150</v>
       </c>
       <c r="F4" t="s">
@@ -2752,14 +2781,14 @@
       <c r="D5" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>151</v>
       </c>
       <c r="F5" t="s">
         <v>184</v>
       </c>
       <c r="G5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2775,7 +2804,7 @@
       <c r="D6" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F6" t="s">
@@ -2798,14 +2827,14 @@
       <c r="D7" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>153</v>
       </c>
       <c r="F7" t="s">
         <v>185</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2821,7 +2850,7 @@
       <c r="D8" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F8" t="s">
@@ -2844,7 +2873,7 @@
       <c r="D9" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F9" t="s">
@@ -2867,7 +2896,7 @@
       <c r="D10" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F10" t="s">
@@ -2890,7 +2919,7 @@
       <c r="D11" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>157</v>
       </c>
       <c r="F11" t="s">
@@ -2913,7 +2942,7 @@
       <c r="D12" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>158</v>
       </c>
       <c r="F12" t="s">
@@ -2936,7 +2965,7 @@
       <c r="D13" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F13" t="s">
@@ -2959,7 +2988,7 @@
       <c r="D14" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>160</v>
       </c>
       <c r="F14" t="s">
@@ -2982,7 +3011,7 @@
       <c r="D15" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>161</v>
       </c>
       <c r="F15" t="s">
@@ -3005,7 +3034,7 @@
       <c r="D16" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F16" t="s">
@@ -3028,14 +3057,14 @@
       <c r="D17" t="s">
         <v>128</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F17" t="s">
         <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3051,7 +3080,7 @@
       <c r="D18" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F18" t="s">
@@ -3074,7 +3103,7 @@
       <c r="D19" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="F19" t="s">
@@ -3097,7 +3126,7 @@
       <c r="D20" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>166</v>
       </c>
       <c r="F20" t="s">
@@ -3120,14 +3149,14 @@
       <c r="D21" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>167</v>
       </c>
       <c r="F21" t="s">
         <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3143,7 +3172,7 @@
       <c r="D22" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F22" t="s">
@@ -3166,7 +3195,7 @@
       <c r="D23" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>169</v>
       </c>
       <c r="F23" t="s">
@@ -3189,7 +3218,7 @@
       <c r="D24" t="s">
         <v>135</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="F24" t="s">
@@ -3212,7 +3241,7 @@
       <c r="D25" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>171</v>
       </c>
       <c r="F25" t="s">
@@ -3235,7 +3264,7 @@
       <c r="D26" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F26" t="s">
@@ -3258,7 +3287,7 @@
       <c r="D27" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F27" t="s">
@@ -3281,7 +3310,7 @@
       <c r="D28" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F28" t="s">
@@ -3304,7 +3333,7 @@
       <c r="D29" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F29" t="s">
@@ -3327,7 +3356,7 @@
       <c r="D30" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>176</v>
       </c>
       <c r="F30" t="s">
@@ -3350,7 +3379,7 @@
       <c r="D31" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>177</v>
       </c>
       <c r="F31" t="s">
@@ -3373,7 +3402,7 @@
       <c r="D32" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>178</v>
       </c>
       <c r="F32" t="s">
@@ -3396,7 +3425,7 @@
       <c r="D33" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>179</v>
       </c>
       <c r="F33" t="s">
@@ -3419,7 +3448,7 @@
       <c r="D34" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>180</v>
       </c>
       <c r="F34" t="s">
@@ -3442,7 +3471,7 @@
       <c r="D35" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>181</v>
       </c>
       <c r="F35" t="s">
@@ -3465,7 +3494,7 @@
       <c r="D36" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>182</v>
       </c>
       <c r="F36" t="s">
@@ -3523,43 +3552,43 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3574,28 +3603,28 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L2" t="s">
         <v>183</v>
@@ -3615,28 +3644,28 @@
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L3" t="s">
         <v>183</v>
@@ -3656,28 +3685,28 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L4" t="s">
         <v>183</v>
@@ -3697,28 +3726,28 @@
         <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L5" t="s">
         <v>183</v>
@@ -3738,28 +3767,28 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L6" t="s">
         <v>183</v>
@@ -3779,28 +3808,28 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L7" t="s">
         <v>184</v>
@@ -3820,28 +3849,28 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L8" t="s">
         <v>184</v>
@@ -3861,28 +3890,28 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L9" t="s">
         <v>184</v>
@@ -3902,28 +3931,28 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L10" t="s">
         <v>184</v>
@@ -3943,28 +3972,28 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L11" t="s">
         <v>185</v>
@@ -3984,28 +4013,28 @@
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L12" t="s">
         <v>185</v>
@@ -4025,28 +4054,28 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L13" t="s">
         <v>185</v>
@@ -4066,28 +4095,28 @@
         <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L14" t="s">
         <v>185</v>
@@ -4107,28 +4136,28 @@
         <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K15" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L15" t="s">
         <v>185</v>
@@ -4148,28 +4177,28 @@
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L16" t="s">
         <v>185</v>
@@ -4189,34 +4218,34 @@
         <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L17" t="s">
         <v>184</v>
       </c>
       <c r="M17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4230,34 +4259,34 @@
         <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I18" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K18" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L18" t="s">
         <v>184</v>
       </c>
       <c r="M18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -4271,34 +4300,34 @@
         <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L19" t="s">
         <v>184</v>
       </c>
       <c r="M19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4312,34 +4341,34 @@
         <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I20" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K20" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L20" t="s">
         <v>184</v>
       </c>
       <c r="M20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4353,34 +4382,34 @@
         <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K21" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L21" t="s">
         <v>184</v>
       </c>
       <c r="M21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4394,34 +4423,34 @@
         <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H22" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I22" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L22" t="s">
         <v>184</v>
       </c>
       <c r="M22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4435,34 +4464,34 @@
         <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H23" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I23" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K23" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L23" t="s">
         <v>184</v>
       </c>
       <c r="M23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -4476,28 +4505,28 @@
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H24" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K24" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L24" t="s">
         <v>185</v>
@@ -4517,28 +4546,28 @@
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G25" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I25" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J25" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K25" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L25" t="s">
         <v>185</v>
@@ -4558,28 +4587,28 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H26" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I26" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K26" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L26" t="s">
         <v>185</v>
@@ -4599,28 +4628,28 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H27" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I27" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J27" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K27" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L27" t="s">
         <v>185</v>
@@ -4640,28 +4669,28 @@
         <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G28" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H28" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I28" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J28" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K28" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L28" t="s">
         <v>185</v>
@@ -4681,34 +4710,34 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F29" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G29" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K29" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L29" t="s">
         <v>185</v>
       </c>
       <c r="M29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -4722,34 +4751,34 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I30" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K30" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L30" t="s">
         <v>185</v>
       </c>
       <c r="M30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4763,34 +4792,34 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G31" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H31" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I31" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K31" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L31" t="s">
         <v>185</v>
       </c>
       <c r="M31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4804,34 +4833,34 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H32" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J32" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K32" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L32" t="s">
         <v>185</v>
       </c>
       <c r="M32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4845,34 +4874,34 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H33" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I33" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J33" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K33" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L33" t="s">
         <v>185</v>
       </c>
       <c r="M33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4886,28 +4915,28 @@
         <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G34" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H34" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I34" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J34" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K34" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L34" t="s">
         <v>185</v>
@@ -4927,28 +4956,28 @@
         <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E35" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H35" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I35" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K35" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L35" t="s">
         <v>185</v>
@@ -4968,28 +4997,28 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H36" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I36" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J36" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K36" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L36" t="s">
         <v>185</v>
@@ -5009,28 +5038,28 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F37" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H37" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I37" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J37" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K37" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L37" t="s">
         <v>185</v>
@@ -5050,28 +5079,28 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F38" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I38" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J38" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K38" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L38" t="s">
         <v>185</v>
@@ -5091,28 +5120,28 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H39" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I39" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J39" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K39" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L39" t="s">
         <v>185</v>
@@ -5132,28 +5161,28 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G40" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I40" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J40" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K40" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L40" t="s">
         <v>185</v>
@@ -5173,28 +5202,28 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H41" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I41" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J41" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K41" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L41" t="s">
         <v>185</v>
@@ -5214,28 +5243,28 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G42" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I42" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J42" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K42" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L42" t="s">
         <v>185</v>
@@ -5255,28 +5284,28 @@
         <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E43" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G43" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H43" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I43" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J43" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K43" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L43" t="s">
         <v>186</v>
@@ -5296,28 +5325,28 @@
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E44" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G44" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H44" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I44" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J44" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K44" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L44" t="s">
         <v>186</v>
@@ -5337,28 +5366,28 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F45" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G45" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H45" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J45" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K45" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L45" t="s">
         <v>186</v>
@@ -5378,28 +5407,28 @@
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E46" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G46" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H46" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I46" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J46" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K46" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L46" t="s">
         <v>186</v>
@@ -5419,28 +5448,28 @@
         <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F47" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G47" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H47" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I47" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J47" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K47" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L47" t="s">
         <v>186</v>
@@ -5460,28 +5489,28 @@
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F48" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H48" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I48" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J48" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K48" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L48" t="s">
         <v>186</v>
@@ -5501,28 +5530,28 @@
         <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F49" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H49" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I49" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J49" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K49" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L49" t="s">
         <v>186</v>
@@ -5542,28 +5571,28 @@
         <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G50" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H50" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J50" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L50" t="s">
         <v>186</v>
@@ -5583,28 +5612,28 @@
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H51" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I51" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J51" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K51" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L51" t="s">
         <v>186</v>
@@ -5624,28 +5653,28 @@
         <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G52" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H52" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I52" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J52" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K52" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L52" t="s">
         <v>186</v>
@@ -5665,28 +5694,28 @@
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G53" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H53" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I53" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J53" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K53" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L53" t="s">
         <v>186</v>
@@ -5706,28 +5735,28 @@
         <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F54" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H54" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I54" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J54" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K54" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L54" t="s">
         <v>187</v>
@@ -5747,28 +5776,28 @@
         <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G55" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H55" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I55" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J55" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K55" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L55" t="s">
         <v>187</v>
@@ -5788,28 +5817,28 @@
         <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H56" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I56" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J56" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K56" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L56" t="s">
         <v>185</v>
@@ -5829,28 +5858,28 @@
         <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H57" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I57" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J57" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K57" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L57" t="s">
         <v>185</v>
@@ -5870,28 +5899,28 @@
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G58" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I58" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J58" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K58" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L58" t="s">
         <v>185</v>
@@ -5911,28 +5940,28 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H59" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I59" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J59" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K59" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L59" t="s">
         <v>184</v>
@@ -5952,28 +5981,28 @@
         <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H60" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I60" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J60" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K60" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L60" t="s">
         <v>184</v>
@@ -5993,28 +6022,28 @@
         <v>53</v>
       </c>
       <c r="D61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H61" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I61" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J61" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K61" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L61" t="s">
         <v>184</v>
@@ -6034,28 +6063,28 @@
         <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F62" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G62" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H62" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I62" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J62" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K62" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L62" t="s">
         <v>184</v>
@@ -6075,28 +6104,28 @@
         <v>53</v>
       </c>
       <c r="D63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F63" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G63" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H63" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I63" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J63" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K63" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L63" t="s">
         <v>184</v>
@@ -6116,28 +6145,28 @@
         <v>53</v>
       </c>
       <c r="D64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G64" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H64" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I64" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J64" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K64" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L64" t="s">
         <v>184</v>
@@ -6157,28 +6186,28 @@
         <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G65" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H65" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I65" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J65" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K65" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L65" t="s">
         <v>184</v>
@@ -6198,28 +6227,28 @@
         <v>53</v>
       </c>
       <c r="D66" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F66" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G66" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H66" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I66" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J66" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K66" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L66" t="s">
         <v>184</v>
@@ -6239,28 +6268,28 @@
         <v>54</v>
       </c>
       <c r="D67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H67" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I67" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J67" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K67" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L67" t="s">
         <v>184</v>
@@ -6280,28 +6309,28 @@
         <v>54</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F68" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H68" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I68" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J68" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K68" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L68" t="s">
         <v>184</v>
@@ -6321,28 +6350,28 @@
         <v>54</v>
       </c>
       <c r="D69" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G69" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H69" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I69" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J69" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K69" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L69" t="s">
         <v>184</v>
@@ -6362,28 +6391,28 @@
         <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G70" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H70" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I70" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J70" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K70" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L70" t="s">
         <v>184</v>
@@ -6403,28 +6432,28 @@
         <v>55</v>
       </c>
       <c r="D71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E71" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H71" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I71" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J71" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K71" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L71" t="s">
         <v>184</v>
@@ -6444,28 +6473,28 @@
         <v>55</v>
       </c>
       <c r="D72" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H72" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I72" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J72" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K72" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L72" t="s">
         <v>184</v>
@@ -6485,28 +6514,28 @@
         <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E73" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H73" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I73" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J73" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K73" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L73" t="s">
         <v>183</v>
@@ -6526,28 +6555,28 @@
         <v>57</v>
       </c>
       <c r="D74" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E74" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F74" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G74" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H74" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I74" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J74" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K74" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L74" t="s">
         <v>185</v>
@@ -6567,28 +6596,28 @@
         <v>57</v>
       </c>
       <c r="D75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G75" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H75" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I75" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J75" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K75" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L75" t="s">
         <v>185</v>
@@ -6608,28 +6637,28 @@
         <v>57</v>
       </c>
       <c r="D76" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E76" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F76" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G76" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H76" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I76" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J76" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K76" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L76" t="s">
         <v>185</v>
@@ -6649,34 +6678,34 @@
         <v>58</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F77" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H77" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I77" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J77" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K77" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L77" t="s">
         <v>187</v>
       </c>
       <c r="M77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6690,34 +6719,34 @@
         <v>58</v>
       </c>
       <c r="D78" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F78" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G78" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I78" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J78" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K78" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L78" t="s">
         <v>187</v>
       </c>
       <c r="M78" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -6731,34 +6760,34 @@
         <v>58</v>
       </c>
       <c r="D79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E79" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G79" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H79" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I79" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J79" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K79" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L79" t="s">
         <v>187</v>
       </c>
       <c r="M79" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -6772,28 +6801,28 @@
         <v>59</v>
       </c>
       <c r="D80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G80" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H80" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I80" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J80" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K80" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L80" t="s">
         <v>185</v>
@@ -6813,28 +6842,28 @@
         <v>59</v>
       </c>
       <c r="D81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H81" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I81" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J81" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K81" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L81" t="s">
         <v>185</v>
@@ -6854,28 +6883,28 @@
         <v>59</v>
       </c>
       <c r="D82" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G82" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H82" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I82" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J82" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K82" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L82" t="s">
         <v>185</v>
@@ -6895,28 +6924,28 @@
         <v>59</v>
       </c>
       <c r="D83" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G83" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H83" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I83" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J83" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K83" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L83" t="s">
         <v>185</v>
@@ -6936,28 +6965,28 @@
         <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E84" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G84" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H84" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I84" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J84" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K84" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L84" t="s">
         <v>185</v>
@@ -6977,28 +7006,28 @@
         <v>60</v>
       </c>
       <c r="D85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G85" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H85" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I85" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J85" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K85" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L85" t="s">
         <v>185</v>
@@ -7018,28 +7047,28 @@
         <v>60</v>
       </c>
       <c r="D86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G86" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H86" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I86" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J86" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K86" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L86" t="s">
         <v>185</v>
@@ -7059,28 +7088,28 @@
         <v>60</v>
       </c>
       <c r="D87" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G87" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H87" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I87" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J87" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K87" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L87" t="s">
         <v>185</v>
@@ -7100,28 +7129,28 @@
         <v>60</v>
       </c>
       <c r="D88" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E88" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G88" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H88" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I88" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J88" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K88" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L88" t="s">
         <v>185</v>
@@ -7141,28 +7170,28 @@
         <v>61</v>
       </c>
       <c r="D89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G89" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H89" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I89" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J89" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K89" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L89" t="s">
         <v>184</v>
@@ -7182,28 +7211,28 @@
         <v>61</v>
       </c>
       <c r="D90" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H90" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I90" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J90" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K90" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L90" t="s">
         <v>184</v>
@@ -7223,28 +7252,28 @@
         <v>61</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H91" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I91" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J91" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K91" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L91" t="s">
         <v>184</v>
@@ -7264,28 +7293,28 @@
         <v>61</v>
       </c>
       <c r="D92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F92" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G92" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H92" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I92" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J92" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K92" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L92" t="s">
         <v>184</v>
@@ -7305,28 +7334,28 @@
         <v>61</v>
       </c>
       <c r="D93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F93" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G93" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H93" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I93" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J93" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K93" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L93" t="s">
         <v>184</v>
@@ -7346,34 +7375,34 @@
         <v>62</v>
       </c>
       <c r="D94" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G94" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H94" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I94" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J94" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K94" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L94" t="s">
         <v>183</v>
       </c>
       <c r="M94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7387,28 +7416,28 @@
         <v>63</v>
       </c>
       <c r="D95" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E95" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I95" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J95" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K95" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L95" t="s">
         <v>185</v>
@@ -7428,28 +7457,28 @@
         <v>63</v>
       </c>
       <c r="D96" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E96" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I96" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J96" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K96" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L96" t="s">
         <v>185</v>
@@ -7469,28 +7498,28 @@
         <v>63</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E97" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F97" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G97" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H97" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I97" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J97" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K97" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L97" t="s">
         <v>185</v>
@@ -7510,28 +7539,28 @@
         <v>64</v>
       </c>
       <c r="D98" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E98" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F98" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G98" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I98" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J98" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K98" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L98" t="s">
         <v>185</v>
@@ -7551,28 +7580,28 @@
         <v>64</v>
       </c>
       <c r="D99" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E99" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H99" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I99" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J99" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K99" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L99" t="s">
         <v>185</v>
@@ -7592,28 +7621,28 @@
         <v>64</v>
       </c>
       <c r="D100" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E100" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H100" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I100" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J100" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K100" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L100" t="s">
         <v>185</v>
@@ -7633,28 +7662,28 @@
         <v>64</v>
       </c>
       <c r="D101" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E101" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G101" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H101" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I101" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J101" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K101" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L101" t="s">
         <v>185</v>
@@ -7674,28 +7703,28 @@
         <v>64</v>
       </c>
       <c r="D102" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H102" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I102" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J102" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K102" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L102" t="s">
         <v>185</v>
@@ -7715,28 +7744,28 @@
         <v>64</v>
       </c>
       <c r="D103" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G103" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H103" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I103" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J103" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K103" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L103" t="s">
         <v>185</v>
@@ -7756,28 +7785,28 @@
         <v>64</v>
       </c>
       <c r="D104" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G104" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I104" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J104" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K104" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L104" t="s">
         <v>185</v>
@@ -7797,28 +7826,28 @@
         <v>65</v>
       </c>
       <c r="D105" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E105" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F105" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H105" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I105" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J105" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K105" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L105" t="s">
         <v>183</v>
@@ -7838,28 +7867,28 @@
         <v>65</v>
       </c>
       <c r="D106" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I106" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J106" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K106" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L106" t="s">
         <v>183</v>
@@ -7879,28 +7908,28 @@
         <v>65</v>
       </c>
       <c r="D107" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E107" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G107" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I107" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J107" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K107" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L107" t="s">
         <v>183</v>
@@ -7920,28 +7949,28 @@
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E108" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G108" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H108" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I108" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J108" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K108" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L108" t="s">
         <v>183</v>
@@ -7961,28 +7990,28 @@
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E109" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G109" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H109" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I109" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J109" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K109" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L109" t="s">
         <v>183</v>
@@ -8002,28 +8031,28 @@
         <v>66</v>
       </c>
       <c r="D110" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H110" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I110" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J110" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K110" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L110" t="s">
         <v>183</v>
@@ -8043,28 +8072,28 @@
         <v>67</v>
       </c>
       <c r="D111" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I111" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J111" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K111" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L111" t="s">
         <v>185</v>
@@ -8084,28 +8113,28 @@
         <v>67</v>
       </c>
       <c r="D112" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E112" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F112" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G112" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H112" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I112" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J112" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K112" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L112" t="s">
         <v>185</v>
@@ -8125,28 +8154,28 @@
         <v>67</v>
       </c>
       <c r="D113" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E113" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F113" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I113" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J113" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K113" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L113" t="s">
         <v>185</v>
@@ -8166,28 +8195,28 @@
         <v>68</v>
       </c>
       <c r="D114" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E114" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H114" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I114" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J114" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K114" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L114" t="s">
         <v>185</v>
@@ -8207,28 +8236,28 @@
         <v>68</v>
       </c>
       <c r="D115" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E115" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G115" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H115" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I115" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J115" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K115" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L115" t="s">
         <v>185</v>
@@ -8248,28 +8277,28 @@
         <v>68</v>
       </c>
       <c r="D116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F116" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G116" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H116" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I116" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J116" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K116" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L116" t="s">
         <v>185</v>
@@ -8289,28 +8318,28 @@
         <v>68</v>
       </c>
       <c r="D117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G117" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H117" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I117" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J117" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K117" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L117" t="s">
         <v>185</v>
@@ -8330,28 +8359,28 @@
         <v>68</v>
       </c>
       <c r="D118" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E118" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F118" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G118" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H118" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I118" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K118" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L118" t="s">
         <v>185</v>
@@ -8371,28 +8400,28 @@
         <v>68</v>
       </c>
       <c r="D119" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H119" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I119" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J119" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K119" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L119" t="s">
         <v>185</v>
@@ -8412,28 +8441,28 @@
         <v>68</v>
       </c>
       <c r="D120" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E120" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F120" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G120" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I120" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J120" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K120" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L120" t="s">
         <v>185</v>
@@ -8453,28 +8482,28 @@
         <v>68</v>
       </c>
       <c r="D121" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E121" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F121" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G121" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I121" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J121" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K121" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L121" t="s">
         <v>185</v>
@@ -8494,28 +8523,28 @@
         <v>68</v>
       </c>
       <c r="D122" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E122" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F122" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I122" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J122" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K122" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L122" t="s">
         <v>185</v>
@@ -8535,28 +8564,28 @@
         <v>68</v>
       </c>
       <c r="D123" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E123" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F123" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G123" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H123" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I123" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J123" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K123" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L123" t="s">
         <v>185</v>
@@ -8576,28 +8605,28 @@
         <v>68</v>
       </c>
       <c r="D124" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E124" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F124" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G124" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H124" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I124" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J124" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K124" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L124" t="s">
         <v>185</v>
@@ -8617,28 +8646,28 @@
         <v>68</v>
       </c>
       <c r="D125" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E125" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G125" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I125" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J125" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K125" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L125" t="s">
         <v>185</v>
@@ -8658,28 +8687,28 @@
         <v>69</v>
       </c>
       <c r="D126" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F126" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G126" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H126" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I126" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J126" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K126" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L126" t="s">
         <v>185</v>
@@ -8699,28 +8728,28 @@
         <v>69</v>
       </c>
       <c r="D127" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E127" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F127" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G127" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H127" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I127" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J127" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K127" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L127" t="s">
         <v>185</v>
@@ -8740,28 +8769,28 @@
         <v>69</v>
       </c>
       <c r="D128" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E128" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F128" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G128" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H128" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I128" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J128" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K128" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L128" t="s">
         <v>185</v>
@@ -8781,28 +8810,28 @@
         <v>69</v>
       </c>
       <c r="D129" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E129" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F129" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G129" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H129" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I129" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J129" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K129" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L129" t="s">
         <v>185</v>
@@ -8822,28 +8851,28 @@
         <v>70</v>
       </c>
       <c r="D130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E130" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F130" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G130" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H130" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I130" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J130" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K130" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L130" t="s">
         <v>187</v>
@@ -8863,28 +8892,28 @@
         <v>70</v>
       </c>
       <c r="D131" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F131" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G131" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H131" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I131" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J131" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K131" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L131" t="s">
         <v>187</v>
@@ -8904,28 +8933,28 @@
         <v>70</v>
       </c>
       <c r="D132" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E132" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F132" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G132" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H132" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I132" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J132" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K132" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L132" t="s">
         <v>187</v>
@@ -8945,28 +8974,28 @@
         <v>70</v>
       </c>
       <c r="D133" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E133" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F133" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G133" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H133" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I133" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J133" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K133" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L133" t="s">
         <v>187</v>
@@ -8986,28 +9015,28 @@
         <v>70</v>
       </c>
       <c r="D134" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E134" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F134" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H134" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I134" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J134" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K134" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L134" t="s">
         <v>187</v>
@@ -9027,28 +9056,28 @@
         <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E135" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G135" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H135" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I135" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J135" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K135" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L135" t="s">
         <v>187</v>
@@ -9068,28 +9097,28 @@
         <v>71</v>
       </c>
       <c r="D136" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E136" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F136" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G136" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H136" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I136" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J136" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K136" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L136" t="s">
         <v>183</v>
@@ -9109,28 +9138,28 @@
         <v>71</v>
       </c>
       <c r="D137" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E137" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F137" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G137" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H137" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J137" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K137" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L137" t="s">
         <v>183</v>
@@ -9150,28 +9179,28 @@
         <v>71</v>
       </c>
       <c r="D138" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E138" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F138" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G138" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H138" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J138" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K138" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L138" t="s">
         <v>183</v>
@@ -9191,28 +9220,28 @@
         <v>71</v>
       </c>
       <c r="D139" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E139" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G139" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J139" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K139" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L139" t="s">
         <v>183</v>
@@ -9232,28 +9261,28 @@
         <v>71</v>
       </c>
       <c r="D140" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E140" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F140" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G140" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H140" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I140" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J140" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K140" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L140" t="s">
         <v>183</v>
@@ -9273,28 +9302,28 @@
         <v>72</v>
       </c>
       <c r="D141" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E141" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F141" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G141" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H141" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I141" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J141" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K141" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L141" t="s">
         <v>185</v>
@@ -9314,28 +9343,28 @@
         <v>72</v>
       </c>
       <c r="D142" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E142" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F142" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G142" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H142" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I142" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J142" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K142" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L142" t="s">
         <v>185</v>
@@ -9355,28 +9384,28 @@
         <v>72</v>
       </c>
       <c r="D143" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E143" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F143" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G143" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H143" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I143" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K143" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L143" t="s">
         <v>185</v>
@@ -9396,28 +9425,28 @@
         <v>72</v>
       </c>
       <c r="D144" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E144" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F144" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H144" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I144" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J144" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K144" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L144" t="s">
         <v>185</v>
@@ -9437,28 +9466,28 @@
         <v>73</v>
       </c>
       <c r="D145" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E145" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F145" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G145" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H145" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I145" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J145" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K145" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L145" t="s">
         <v>185</v>
@@ -9478,28 +9507,28 @@
         <v>73</v>
       </c>
       <c r="D146" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E146" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F146" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H146" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I146" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J146" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K146" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L146" t="s">
         <v>185</v>
@@ -9519,28 +9548,28 @@
         <v>73</v>
       </c>
       <c r="D147" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E147" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G147" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H147" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I147" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J147" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K147" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L147" t="s">
         <v>185</v>
@@ -9560,28 +9589,28 @@
         <v>74</v>
       </c>
       <c r="D148" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E148" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F148" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G148" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H148" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I148" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J148" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K148" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L148" t="s">
         <v>185</v>
@@ -9601,28 +9630,28 @@
         <v>74</v>
       </c>
       <c r="D149" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G149" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H149" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I149" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J149" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K149" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L149" t="s">
         <v>185</v>
@@ -9642,28 +9671,28 @@
         <v>74</v>
       </c>
       <c r="D150" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E150" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F150" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G150" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H150" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I150" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J150" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K150" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L150" t="s">
         <v>185</v>
@@ -9683,28 +9712,28 @@
         <v>74</v>
       </c>
       <c r="D151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F151" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G151" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H151" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I151" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J151" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K151" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L151" t="s">
         <v>185</v>
@@ -9724,28 +9753,28 @@
         <v>74</v>
       </c>
       <c r="D152" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F152" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G152" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H152" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I152" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J152" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K152" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L152" t="s">
         <v>185</v>
@@ -9765,28 +9794,28 @@
         <v>75</v>
       </c>
       <c r="D153" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E153" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F153" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G153" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H153" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I153" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J153" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K153" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L153" t="s">
         <v>185</v>
@@ -9806,28 +9835,28 @@
         <v>75</v>
       </c>
       <c r="D154" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E154" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G154" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H154" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J154" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K154" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="L154" t="s">
         <v>185</v>
@@ -9847,28 +9876,28 @@
         <v>75</v>
       </c>
       <c r="D155" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E155" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F155" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G155" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H155" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I155" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J155" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K155" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L155" t="s">
         <v>185</v>
@@ -9888,28 +9917,28 @@
         <v>75</v>
       </c>
       <c r="D156" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E156" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F156" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G156" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H156" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I156" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J156" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K156" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L156" t="s">
         <v>185</v>
@@ -9929,28 +9958,28 @@
         <v>75</v>
       </c>
       <c r="D157" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E157" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F157" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G157" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H157" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I157" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J157" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K157" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L157" t="s">
         <v>185</v>
@@ -9970,28 +9999,28 @@
         <v>75</v>
       </c>
       <c r="D158" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E158" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F158" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G158" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I158" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J158" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K158" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L158" t="s">
         <v>185</v>
@@ -10011,28 +10040,28 @@
         <v>75</v>
       </c>
       <c r="D159" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E159" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F159" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G159" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H159" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I159" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J159" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K159" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L159" t="s">
         <v>185</v>
@@ -10052,28 +10081,28 @@
         <v>76</v>
       </c>
       <c r="D160" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E160" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F160" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H160" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I160" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J160" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K160" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L160" t="s">
         <v>185</v>
@@ -10093,28 +10122,28 @@
         <v>76</v>
       </c>
       <c r="D161" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E161" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G161" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H161" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I161" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J161" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K161" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L161" t="s">
         <v>185</v>
@@ -10134,28 +10163,28 @@
         <v>76</v>
       </c>
       <c r="D162" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E162" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F162" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G162" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H162" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I162" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J162" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K162" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L162" t="s">
         <v>185</v>
@@ -10175,28 +10204,28 @@
         <v>76</v>
       </c>
       <c r="D163" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E163" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F163" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G163" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H163" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I163" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J163" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K163" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L163" t="s">
         <v>185</v>
@@ -10216,28 +10245,28 @@
         <v>76</v>
       </c>
       <c r="D164" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E164" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F164" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G164" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I164" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J164" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K164" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L164" t="s">
         <v>185</v>
@@ -10257,28 +10286,28 @@
         <v>77</v>
       </c>
       <c r="D165" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E165" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F165" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G165" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H165" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I165" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K165" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L165" t="s">
         <v>185</v>
@@ -10298,28 +10327,28 @@
         <v>77</v>
       </c>
       <c r="D166" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E166" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F166" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G166" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H166" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I166" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J166" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K166" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L166" t="s">
         <v>185</v>
@@ -10339,28 +10368,28 @@
         <v>77</v>
       </c>
       <c r="D167" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E167" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F167" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G167" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H167" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I167" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J167" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K167" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L167" t="s">
         <v>185</v>

--- a/excel-files/atlas-mitigations.xlsx
+++ b/excel-files/atlas-mitigations.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="736">
   <si>
     <t>ID</t>
   </si>
@@ -616,6 +616,9 @@
   </si>
   <si>
     <t>19 March 2026</t>
+  </si>
+  <si>
+    <t>22 April 2026</t>
   </si>
   <si>
     <t>18 December 2025</t>
@@ -2903,7 +2906,7 @@
         <v>187</v>
       </c>
       <c r="G10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3064,7 +3067,7 @@
         <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3156,7 +3159,7 @@
         <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3432,7 +3435,7 @@
         <v>185</v>
       </c>
       <c r="G33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3553,34 +3556,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1</v>
@@ -3603,28 +3606,28 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L2" t="s">
         <v>183</v>
@@ -3644,28 +3647,28 @@
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L3" t="s">
         <v>183</v>
@@ -3685,28 +3688,28 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L4" t="s">
         <v>183</v>
@@ -3726,28 +3729,28 @@
         <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L5" t="s">
         <v>183</v>
@@ -3767,28 +3770,28 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L6" t="s">
         <v>183</v>
@@ -3808,28 +3811,28 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L7" t="s">
         <v>184</v>
@@ -3849,28 +3852,28 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L8" t="s">
         <v>184</v>
@@ -3890,28 +3893,28 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L9" t="s">
         <v>184</v>
@@ -3931,28 +3934,28 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L10" t="s">
         <v>184</v>
@@ -3972,28 +3975,28 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L11" t="s">
         <v>185</v>
@@ -4013,28 +4016,28 @@
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L12" t="s">
         <v>185</v>
@@ -4054,28 +4057,28 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K13" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L13" t="s">
         <v>185</v>
@@ -4095,28 +4098,28 @@
         <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K14" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L14" t="s">
         <v>185</v>
@@ -4136,28 +4139,28 @@
         <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I15" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K15" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L15" t="s">
         <v>185</v>
@@ -4177,28 +4180,28 @@
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L16" t="s">
         <v>185</v>
@@ -4218,28 +4221,28 @@
         <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L17" t="s">
         <v>184</v>
@@ -4259,28 +4262,28 @@
         <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K18" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L18" t="s">
         <v>184</v>
@@ -4300,28 +4303,28 @@
         <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L19" t="s">
         <v>184</v>
@@ -4341,28 +4344,28 @@
         <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J20" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K20" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L20" t="s">
         <v>184</v>
@@ -4382,28 +4385,28 @@
         <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G21" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I21" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L21" t="s">
         <v>184</v>
@@ -4423,28 +4426,28 @@
         <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J22" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L22" t="s">
         <v>184</v>
@@ -4464,28 +4467,28 @@
         <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I23" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J23" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K23" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L23" t="s">
         <v>184</v>
@@ -4505,28 +4508,28 @@
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G24" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H24" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I24" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J24" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K24" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L24" t="s">
         <v>185</v>
@@ -4546,28 +4549,28 @@
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G25" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K25" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L25" t="s">
         <v>185</v>
@@ -4587,28 +4590,28 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H26" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I26" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J26" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K26" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L26" t="s">
         <v>185</v>
@@ -4628,28 +4631,28 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H27" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J27" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K27" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L27" t="s">
         <v>185</v>
@@ -4669,28 +4672,28 @@
         <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I28" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J28" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K28" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L28" t="s">
         <v>185</v>
@@ -4710,28 +4713,28 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I29" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J29" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K29" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L29" t="s">
         <v>185</v>
@@ -4751,28 +4754,28 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H30" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I30" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J30" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K30" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L30" t="s">
         <v>185</v>
@@ -4792,28 +4795,28 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I31" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K31" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L31" t="s">
         <v>185</v>
@@ -4833,28 +4836,28 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J32" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K32" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L32" t="s">
         <v>185</v>
@@ -4874,28 +4877,28 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F33" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I33" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J33" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K33" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L33" t="s">
         <v>185</v>
@@ -4915,28 +4918,28 @@
         <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G34" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I34" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J34" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K34" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L34" t="s">
         <v>185</v>
@@ -4956,28 +4959,28 @@
         <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G35" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I35" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J35" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K35" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L35" t="s">
         <v>185</v>
@@ -4997,28 +5000,28 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H36" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I36" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J36" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K36" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L36" t="s">
         <v>185</v>
@@ -5038,28 +5041,28 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H37" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I37" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J37" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K37" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L37" t="s">
         <v>185</v>
@@ -5079,28 +5082,28 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I38" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J38" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K38" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L38" t="s">
         <v>185</v>
@@ -5120,28 +5123,28 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I39" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J39" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K39" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L39" t="s">
         <v>185</v>
@@ -5161,28 +5164,28 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G40" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I40" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J40" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K40" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L40" t="s">
         <v>185</v>
@@ -5202,28 +5205,28 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H41" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I41" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J41" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K41" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L41" t="s">
         <v>185</v>
@@ -5243,28 +5246,28 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G42" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H42" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I42" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J42" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K42" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L42" t="s">
         <v>185</v>
@@ -5284,28 +5287,28 @@
         <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I43" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J43" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K43" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L43" t="s">
         <v>186</v>
@@ -5325,28 +5328,28 @@
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G44" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H44" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I44" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J44" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K44" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L44" t="s">
         <v>186</v>
@@ -5366,28 +5369,28 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G45" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H45" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I45" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J45" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K45" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L45" t="s">
         <v>186</v>
@@ -5407,28 +5410,28 @@
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F46" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G46" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H46" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I46" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J46" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K46" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L46" t="s">
         <v>186</v>
@@ -5448,28 +5451,28 @@
         <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F47" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G47" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H47" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I47" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J47" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K47" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L47" t="s">
         <v>186</v>
@@ -5489,28 +5492,28 @@
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E48" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H48" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I48" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J48" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K48" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L48" t="s">
         <v>186</v>
@@ -5530,28 +5533,28 @@
         <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G49" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I49" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J49" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K49" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L49" t="s">
         <v>186</v>
@@ -5571,28 +5574,28 @@
         <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H50" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I50" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J50" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L50" t="s">
         <v>186</v>
@@ -5612,28 +5615,28 @@
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G51" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H51" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I51" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J51" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K51" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L51" t="s">
         <v>186</v>
@@ -5653,28 +5656,28 @@
         <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G52" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H52" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I52" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J52" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K52" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L52" t="s">
         <v>186</v>
@@ -5694,28 +5697,28 @@
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E53" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G53" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H53" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I53" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J53" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K53" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L53" t="s">
         <v>186</v>
@@ -5735,34 +5738,34 @@
         <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F54" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I54" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J54" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K54" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L54" t="s">
         <v>187</v>
       </c>
       <c r="M54" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -5776,34 +5779,34 @@
         <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H55" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I55" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J55" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K55" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L55" t="s">
         <v>187</v>
       </c>
       <c r="M55" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -5817,28 +5820,28 @@
         <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H56" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I56" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J56" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K56" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L56" t="s">
         <v>185</v>
@@ -5858,28 +5861,28 @@
         <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H57" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I57" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J57" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K57" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L57" t="s">
         <v>185</v>
@@ -5899,28 +5902,28 @@
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F58" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G58" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H58" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I58" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J58" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K58" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L58" t="s">
         <v>185</v>
@@ -5940,28 +5943,28 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G59" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H59" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I59" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J59" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K59" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L59" t="s">
         <v>184</v>
@@ -5981,28 +5984,28 @@
         <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H60" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I60" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J60" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K60" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L60" t="s">
         <v>184</v>
@@ -6022,28 +6025,28 @@
         <v>53</v>
       </c>
       <c r="D61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G61" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H61" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I61" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J61" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K61" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L61" t="s">
         <v>184</v>
@@ -6063,28 +6066,28 @@
         <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F62" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G62" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H62" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I62" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J62" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K62" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L62" t="s">
         <v>184</v>
@@ -6104,28 +6107,28 @@
         <v>53</v>
       </c>
       <c r="D63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F63" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G63" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H63" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I63" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J63" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K63" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L63" t="s">
         <v>184</v>
@@ -6145,28 +6148,28 @@
         <v>53</v>
       </c>
       <c r="D64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G64" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H64" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I64" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J64" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K64" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L64" t="s">
         <v>184</v>
@@ -6186,28 +6189,28 @@
         <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G65" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H65" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I65" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J65" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K65" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L65" t="s">
         <v>184</v>
@@ -6227,28 +6230,28 @@
         <v>53</v>
       </c>
       <c r="D66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G66" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H66" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I66" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J66" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K66" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L66" t="s">
         <v>184</v>
@@ -6268,28 +6271,28 @@
         <v>54</v>
       </c>
       <c r="D67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G67" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H67" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I67" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J67" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K67" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L67" t="s">
         <v>184</v>
@@ -6309,28 +6312,28 @@
         <v>54</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I68" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J68" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K68" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L68" t="s">
         <v>184</v>
@@ -6350,28 +6353,28 @@
         <v>54</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H69" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I69" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J69" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K69" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L69" t="s">
         <v>184</v>
@@ -6391,28 +6394,28 @@
         <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G70" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H70" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J70" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K70" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L70" t="s">
         <v>184</v>
@@ -6432,28 +6435,28 @@
         <v>55</v>
       </c>
       <c r="D71" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G71" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I71" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J71" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K71" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L71" t="s">
         <v>184</v>
@@ -6473,28 +6476,28 @@
         <v>55</v>
       </c>
       <c r="D72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H72" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I72" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J72" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K72" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L72" t="s">
         <v>184</v>
@@ -6514,28 +6517,28 @@
         <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H73" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I73" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J73" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K73" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L73" t="s">
         <v>183</v>
@@ -6555,28 +6558,28 @@
         <v>57</v>
       </c>
       <c r="D74" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G74" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H74" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I74" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J74" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K74" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L74" t="s">
         <v>185</v>
@@ -6596,28 +6599,28 @@
         <v>57</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F75" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G75" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H75" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I75" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J75" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K75" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L75" t="s">
         <v>185</v>
@@ -6637,28 +6640,28 @@
         <v>57</v>
       </c>
       <c r="D76" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E76" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G76" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H76" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I76" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J76" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K76" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L76" t="s">
         <v>185</v>
@@ -6678,34 +6681,34 @@
         <v>58</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E77" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I77" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J77" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K77" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L77" t="s">
         <v>187</v>
       </c>
       <c r="M77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6719,34 +6722,34 @@
         <v>58</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I78" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J78" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K78" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L78" t="s">
         <v>187</v>
       </c>
       <c r="M78" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -6760,34 +6763,34 @@
         <v>58</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H79" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I79" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J79" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K79" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L79" t="s">
         <v>187</v>
       </c>
       <c r="M79" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -6801,28 +6804,28 @@
         <v>59</v>
       </c>
       <c r="D80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F80" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H80" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I80" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J80" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K80" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L80" t="s">
         <v>185</v>
@@ -6842,28 +6845,28 @@
         <v>59</v>
       </c>
       <c r="D81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H81" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I81" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J81" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K81" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L81" t="s">
         <v>185</v>
@@ -6883,28 +6886,28 @@
         <v>59</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F82" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G82" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H82" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I82" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J82" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K82" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L82" t="s">
         <v>185</v>
@@ -6924,28 +6927,28 @@
         <v>59</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G83" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H83" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I83" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J83" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K83" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L83" t="s">
         <v>185</v>
@@ -6965,28 +6968,28 @@
         <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G84" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H84" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I84" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J84" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K84" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L84" t="s">
         <v>185</v>
@@ -7006,28 +7009,28 @@
         <v>60</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G85" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H85" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I85" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J85" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K85" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L85" t="s">
         <v>185</v>
@@ -7047,28 +7050,28 @@
         <v>60</v>
       </c>
       <c r="D86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E86" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G86" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H86" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I86" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J86" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K86" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L86" t="s">
         <v>185</v>
@@ -7088,28 +7091,28 @@
         <v>60</v>
       </c>
       <c r="D87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G87" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H87" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I87" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J87" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K87" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L87" t="s">
         <v>185</v>
@@ -7129,28 +7132,28 @@
         <v>60</v>
       </c>
       <c r="D88" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E88" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G88" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H88" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I88" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J88" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K88" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L88" t="s">
         <v>185</v>
@@ -7170,28 +7173,28 @@
         <v>61</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E89" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G89" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H89" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I89" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J89" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K89" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L89" t="s">
         <v>184</v>
@@ -7211,28 +7214,28 @@
         <v>61</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G90" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H90" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I90" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J90" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K90" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L90" t="s">
         <v>184</v>
@@ -7252,28 +7255,28 @@
         <v>61</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G91" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H91" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I91" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J91" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K91" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L91" t="s">
         <v>184</v>
@@ -7293,28 +7296,28 @@
         <v>61</v>
       </c>
       <c r="D92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F92" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G92" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H92" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I92" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J92" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K92" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L92" t="s">
         <v>184</v>
@@ -7334,28 +7337,28 @@
         <v>61</v>
       </c>
       <c r="D93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G93" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H93" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I93" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J93" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K93" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L93" t="s">
         <v>184</v>
@@ -7375,34 +7378,34 @@
         <v>62</v>
       </c>
       <c r="D94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E94" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G94" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H94" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I94" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J94" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K94" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L94" t="s">
         <v>183</v>
       </c>
       <c r="M94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7416,28 +7419,28 @@
         <v>63</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F95" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I95" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J95" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K95" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L95" t="s">
         <v>185</v>
@@ -7457,28 +7460,28 @@
         <v>63</v>
       </c>
       <c r="D96" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F96" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G96" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I96" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J96" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K96" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L96" t="s">
         <v>185</v>
@@ -7498,28 +7501,28 @@
         <v>63</v>
       </c>
       <c r="D97" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F97" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G97" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H97" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I97" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J97" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K97" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L97" t="s">
         <v>185</v>
@@ -7539,28 +7542,28 @@
         <v>64</v>
       </c>
       <c r="D98" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F98" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G98" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H98" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I98" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J98" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K98" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L98" t="s">
         <v>185</v>
@@ -7580,28 +7583,28 @@
         <v>64</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H99" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I99" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J99" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K99" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L99" t="s">
         <v>185</v>
@@ -7621,28 +7624,28 @@
         <v>64</v>
       </c>
       <c r="D100" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E100" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F100" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G100" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H100" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I100" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J100" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K100" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L100" t="s">
         <v>185</v>
@@ -7662,28 +7665,28 @@
         <v>64</v>
       </c>
       <c r="D101" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E101" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F101" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G101" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H101" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I101" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J101" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K101" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L101" t="s">
         <v>185</v>
@@ -7703,28 +7706,28 @@
         <v>64</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G102" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H102" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I102" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J102" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K102" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L102" t="s">
         <v>185</v>
@@ -7744,28 +7747,28 @@
         <v>64</v>
       </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F103" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H103" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I103" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J103" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K103" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L103" t="s">
         <v>185</v>
@@ -7785,28 +7788,28 @@
         <v>64</v>
       </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F104" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I104" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J104" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K104" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L104" t="s">
         <v>185</v>
@@ -7826,28 +7829,28 @@
         <v>65</v>
       </c>
       <c r="D105" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E105" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F105" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G105" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H105" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I105" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J105" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K105" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L105" t="s">
         <v>183</v>
@@ -7867,28 +7870,28 @@
         <v>65</v>
       </c>
       <c r="D106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E106" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G106" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I106" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J106" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K106" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L106" t="s">
         <v>183</v>
@@ -7908,28 +7911,28 @@
         <v>65</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E107" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F107" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G107" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H107" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I107" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J107" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K107" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L107" t="s">
         <v>183</v>
@@ -7949,28 +7952,28 @@
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E108" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F108" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G108" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H108" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I108" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J108" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K108" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L108" t="s">
         <v>183</v>
@@ -7990,28 +7993,28 @@
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E109" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G109" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H109" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I109" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J109" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K109" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L109" t="s">
         <v>183</v>
@@ -8031,28 +8034,28 @@
         <v>66</v>
       </c>
       <c r="D110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H110" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I110" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J110" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K110" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L110" t="s">
         <v>183</v>
@@ -8072,28 +8075,28 @@
         <v>67</v>
       </c>
       <c r="D111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E111" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F111" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I111" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J111" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K111" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L111" t="s">
         <v>185</v>
@@ -8113,28 +8116,28 @@
         <v>67</v>
       </c>
       <c r="D112" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E112" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G112" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I112" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J112" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K112" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L112" t="s">
         <v>185</v>
@@ -8154,28 +8157,28 @@
         <v>67</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E113" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F113" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H113" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I113" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J113" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K113" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L113" t="s">
         <v>185</v>
@@ -8195,28 +8198,28 @@
         <v>68</v>
       </c>
       <c r="D114" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E114" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F114" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G114" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H114" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I114" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J114" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K114" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L114" t="s">
         <v>185</v>
@@ -8236,28 +8239,28 @@
         <v>68</v>
       </c>
       <c r="D115" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E115" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F115" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H115" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I115" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J115" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K115" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L115" t="s">
         <v>185</v>
@@ -8277,28 +8280,28 @@
         <v>68</v>
       </c>
       <c r="D116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E116" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F116" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G116" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H116" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I116" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J116" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K116" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L116" t="s">
         <v>185</v>
@@ -8318,28 +8321,28 @@
         <v>68</v>
       </c>
       <c r="D117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F117" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G117" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H117" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I117" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J117" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K117" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L117" t="s">
         <v>185</v>
@@ -8359,28 +8362,28 @@
         <v>68</v>
       </c>
       <c r="D118" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F118" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H118" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I118" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J118" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K118" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L118" t="s">
         <v>185</v>
@@ -8400,28 +8403,28 @@
         <v>68</v>
       </c>
       <c r="D119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E119" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F119" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G119" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H119" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I119" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J119" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K119" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L119" t="s">
         <v>185</v>
@@ -8441,28 +8444,28 @@
         <v>68</v>
       </c>
       <c r="D120" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F120" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G120" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I120" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J120" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K120" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L120" t="s">
         <v>185</v>
@@ -8482,28 +8485,28 @@
         <v>68</v>
       </c>
       <c r="D121" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E121" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F121" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G121" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H121" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I121" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J121" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K121" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L121" t="s">
         <v>185</v>
@@ -8523,28 +8526,28 @@
         <v>68</v>
       </c>
       <c r="D122" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E122" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F122" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I122" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J122" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K122" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L122" t="s">
         <v>185</v>
@@ -8564,28 +8567,28 @@
         <v>68</v>
       </c>
       <c r="D123" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E123" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F123" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G123" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H123" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I123" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J123" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K123" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L123" t="s">
         <v>185</v>
@@ -8605,28 +8608,28 @@
         <v>68</v>
       </c>
       <c r="D124" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E124" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F124" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G124" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H124" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I124" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J124" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K124" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L124" t="s">
         <v>185</v>
@@ -8646,28 +8649,28 @@
         <v>68</v>
       </c>
       <c r="D125" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E125" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F125" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G125" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I125" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J125" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K125" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L125" t="s">
         <v>185</v>
@@ -8687,28 +8690,28 @@
         <v>69</v>
       </c>
       <c r="D126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E126" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F126" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G126" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I126" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J126" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K126" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L126" t="s">
         <v>185</v>
@@ -8728,28 +8731,28 @@
         <v>69</v>
       </c>
       <c r="D127" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E127" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G127" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I127" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J127" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K127" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L127" t="s">
         <v>185</v>
@@ -8769,28 +8772,28 @@
         <v>69</v>
       </c>
       <c r="D128" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E128" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F128" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G128" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I128" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J128" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K128" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L128" t="s">
         <v>185</v>
@@ -8810,28 +8813,28 @@
         <v>69</v>
       </c>
       <c r="D129" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E129" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F129" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G129" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H129" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I129" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J129" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K129" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L129" t="s">
         <v>185</v>
@@ -8851,28 +8854,28 @@
         <v>70</v>
       </c>
       <c r="D130" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E130" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F130" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G130" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H130" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I130" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J130" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K130" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L130" t="s">
         <v>187</v>
@@ -8892,28 +8895,28 @@
         <v>70</v>
       </c>
       <c r="D131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E131" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F131" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H131" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I131" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J131" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K131" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L131" t="s">
         <v>187</v>
@@ -8933,28 +8936,28 @@
         <v>70</v>
       </c>
       <c r="D132" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F132" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H132" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I132" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J132" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K132" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L132" t="s">
         <v>187</v>
@@ -8974,28 +8977,28 @@
         <v>70</v>
       </c>
       <c r="D133" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E133" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F133" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G133" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H133" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I133" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J133" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K133" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L133" t="s">
         <v>187</v>
@@ -9015,28 +9018,28 @@
         <v>70</v>
       </c>
       <c r="D134" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E134" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F134" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G134" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H134" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I134" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J134" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K134" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L134" t="s">
         <v>187</v>
@@ -9056,28 +9059,28 @@
         <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E135" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F135" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G135" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H135" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I135" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J135" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K135" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L135" t="s">
         <v>187</v>
@@ -9097,28 +9100,28 @@
         <v>71</v>
       </c>
       <c r="D136" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E136" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F136" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H136" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I136" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J136" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K136" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L136" t="s">
         <v>183</v>
@@ -9138,28 +9141,28 @@
         <v>71</v>
       </c>
       <c r="D137" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E137" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F137" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H137" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I137" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J137" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K137" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L137" t="s">
         <v>183</v>
@@ -9179,28 +9182,28 @@
         <v>71</v>
       </c>
       <c r="D138" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E138" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F138" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G138" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H138" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I138" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J138" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K138" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L138" t="s">
         <v>183</v>
@@ -9220,28 +9223,28 @@
         <v>71</v>
       </c>
       <c r="D139" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E139" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F139" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G139" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H139" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J139" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K139" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L139" t="s">
         <v>183</v>
@@ -9261,28 +9264,28 @@
         <v>71</v>
       </c>
       <c r="D140" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E140" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F140" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G140" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H140" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J140" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K140" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L140" t="s">
         <v>183</v>
@@ -9302,28 +9305,28 @@
         <v>72</v>
       </c>
       <c r="D141" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E141" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F141" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G141" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H141" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I141" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J141" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K141" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L141" t="s">
         <v>185</v>
@@ -9343,28 +9346,28 @@
         <v>72</v>
       </c>
       <c r="D142" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E142" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F142" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G142" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H142" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I142" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J142" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K142" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L142" t="s">
         <v>185</v>
@@ -9384,28 +9387,28 @@
         <v>72</v>
       </c>
       <c r="D143" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E143" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F143" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G143" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H143" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I143" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J143" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K143" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L143" t="s">
         <v>185</v>
@@ -9425,28 +9428,28 @@
         <v>72</v>
       </c>
       <c r="D144" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E144" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F144" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G144" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H144" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I144" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J144" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K144" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L144" t="s">
         <v>185</v>
@@ -9466,28 +9469,28 @@
         <v>73</v>
       </c>
       <c r="D145" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E145" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F145" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G145" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H145" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I145" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J145" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K145" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L145" t="s">
         <v>185</v>
@@ -9507,28 +9510,28 @@
         <v>73</v>
       </c>
       <c r="D146" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E146" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F146" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H146" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I146" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J146" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K146" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L146" t="s">
         <v>185</v>
@@ -9548,28 +9551,28 @@
         <v>73</v>
       </c>
       <c r="D147" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E147" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F147" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G147" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H147" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I147" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J147" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K147" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L147" t="s">
         <v>185</v>
@@ -9589,34 +9592,34 @@
         <v>74</v>
       </c>
       <c r="D148" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E148" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F148" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G148" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H148" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I148" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J148" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K148" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L148" t="s">
         <v>185</v>
       </c>
       <c r="M148" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -9630,34 +9633,34 @@
         <v>74</v>
       </c>
       <c r="D149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E149" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G149" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H149" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I149" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J149" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K149" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L149" t="s">
         <v>185</v>
       </c>
       <c r="M149" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -9671,34 +9674,34 @@
         <v>74</v>
       </c>
       <c r="D150" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E150" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F150" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G150" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H150" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I150" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J150" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K150" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L150" t="s">
         <v>185</v>
       </c>
       <c r="M150" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -9712,34 +9715,34 @@
         <v>74</v>
       </c>
       <c r="D151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F151" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G151" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H151" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I151" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J151" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K151" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L151" t="s">
         <v>185</v>
       </c>
       <c r="M151" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -9753,34 +9756,34 @@
         <v>74</v>
       </c>
       <c r="D152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F152" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G152" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H152" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I152" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J152" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K152" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L152" t="s">
         <v>185</v>
       </c>
       <c r="M152" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -9794,28 +9797,28 @@
         <v>75</v>
       </c>
       <c r="D153" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E153" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F153" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G153" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H153" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I153" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J153" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K153" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="L153" t="s">
         <v>185</v>
@@ -9835,28 +9838,28 @@
         <v>75</v>
       </c>
       <c r="D154" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E154" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G154" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H154" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I154" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J154" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K154" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L154" t="s">
         <v>185</v>
@@ -9876,28 +9879,28 @@
         <v>75</v>
       </c>
       <c r="D155" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E155" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F155" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G155" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H155" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I155" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J155" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K155" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L155" t="s">
         <v>185</v>
@@ -9917,28 +9920,28 @@
         <v>75</v>
       </c>
       <c r="D156" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E156" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F156" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G156" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H156" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I156" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J156" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K156" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L156" t="s">
         <v>185</v>
@@ -9958,28 +9961,28 @@
         <v>75</v>
       </c>
       <c r="D157" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E157" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F157" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G157" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H157" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I157" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J157" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K157" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L157" t="s">
         <v>185</v>
@@ -9999,28 +10002,28 @@
         <v>75</v>
       </c>
       <c r="D158" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E158" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F158" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G158" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H158" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I158" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J158" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K158" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L158" t="s">
         <v>185</v>
@@ -10040,28 +10043,28 @@
         <v>75</v>
       </c>
       <c r="D159" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E159" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F159" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G159" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H159" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I159" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J159" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K159" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L159" t="s">
         <v>185</v>
@@ -10081,28 +10084,28 @@
         <v>76</v>
       </c>
       <c r="D160" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E160" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F160" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G160" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H160" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I160" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J160" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K160" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L160" t="s">
         <v>185</v>
@@ -10122,28 +10125,28 @@
         <v>76</v>
       </c>
       <c r="D161" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E161" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F161" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G161" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H161" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I161" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J161" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K161" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L161" t="s">
         <v>185</v>
@@ -10163,28 +10166,28 @@
         <v>76</v>
       </c>
       <c r="D162" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E162" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F162" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G162" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H162" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I162" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J162" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K162" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L162" t="s">
         <v>185</v>
@@ -10204,28 +10207,28 @@
         <v>76</v>
       </c>
       <c r="D163" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E163" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F163" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G163" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H163" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I163" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J163" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K163" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L163" t="s">
         <v>185</v>
@@ -10245,28 +10248,28 @@
         <v>76</v>
       </c>
       <c r="D164" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E164" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F164" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G164" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H164" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I164" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J164" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K164" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L164" t="s">
         <v>185</v>
@@ -10286,28 +10289,28 @@
         <v>77</v>
       </c>
       <c r="D165" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E165" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F165" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G165" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H165" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I165" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J165" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K165" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L165" t="s">
         <v>185</v>
@@ -10327,28 +10330,28 @@
         <v>77</v>
       </c>
       <c r="D166" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E166" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F166" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G166" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H166" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I166" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J166" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K166" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L166" t="s">
         <v>185</v>
@@ -10368,28 +10371,28 @@
         <v>77</v>
       </c>
       <c r="D167" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E167" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F167" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G167" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H167" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I167" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J167" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K167" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L167" t="s">
         <v>185</v>
